--- a/Paper/Dummy Example/Analysis.xlsx
+++ b/Paper/Dummy Example/Analysis.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sidshah/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sidshah/Library/Mobile Documents/com~apple~CloudDocs/Projects/Research Assistantship with Pinsky/MAD Portfolio Construction/Paper/Dummy Example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40FEF0E-678A-1448-9619-77D2C36E38C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B075EBE-68CE-5943-B969-869316822132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{C006080D-DBCC-4845-B864-19D48DF306C2}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C006080D-DBCC-4845-B864-19D48DF306C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>Day</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Daily Returns</t>
   </si>
   <si>
-    <t>Mean</t>
-  </si>
-  <si>
     <t>MAD</t>
   </si>
   <si>
@@ -100,15 +97,23 @@
   </si>
   <si>
     <t>Ann. Risk</t>
+  </si>
+  <si>
+    <t>Weekly Risk</t>
+  </si>
+  <si>
+    <t>Mean Return</t>
+  </si>
+  <si>
+    <t>Weekly MAD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -126,12 +131,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -148,22 +159,21 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -500,43 +510,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EE203B-71D4-E14C-9298-AB41D84ED2A8}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="5"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.03</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" t="s">
@@ -553,154 +577,153 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4">
         <v>2</v>
       </c>
+      <c r="B4" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.02</v>
+      </c>
       <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="3">
-        <f>AVERAGE(B5:B9)</f>
+        <v>14</v>
+      </c>
+      <c r="F4" s="2">
+        <f>AVERAGE(B3:B7)</f>
         <v>0.02</v>
       </c>
-      <c r="G4" s="3">
-        <f>AVERAGE(C5:C9)</f>
+      <c r="G4" s="2">
+        <f>AVERAGE(C3:C7)</f>
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H4" s="5">
-        <f>AVERAGE(B5:B9)</f>
+      <c r="H4" s="3">
+        <f>AVERAGE(B3:B7)</f>
         <v>0.02</v>
       </c>
-      <c r="I4" s="5">
-        <f>AVERAGE(C5:C9)</f>
+      <c r="I4" s="3">
+        <f>AVERAGE(C3:C7)</f>
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="8">
-        <v>0.03</v>
-      </c>
-      <c r="D5" s="3"/>
+      <c r="C5" s="7">
+        <v>-0.01</v>
+      </c>
+      <c r="D5" s="2"/>
       <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" cm="1">
-        <f t="array" ref="F5">AVERAGE(ABS(B5:B9- $F$4)) * (250)^0.5</f>
-        <v>0.12649110640673519</v>
-      </c>
-      <c r="G5" s="3" cm="1">
-        <f t="array" ref="G5">AVERAGE(ABS(C5:C9- $F$4)) * (250)^0.5</f>
-        <v>0.22135943621178653</v>
-      </c>
-      <c r="H5" s="3" cm="1">
-        <f t="array" ref="H5">AVERAGE((B5:B9 - H$4)^2) ^ 0.5 * (250)^0.5</f>
-        <v>0.16583123951776998</v>
-      </c>
-      <c r="I5" s="3" cm="1">
-        <f t="array" ref="I5">AVERAGE((C5:C9 - I$4)^2) ^ 0.5 * (250)^0.5</f>
-        <v>0.28548204847240399</v>
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" cm="1">
+        <f t="array" ref="F5">AVERAGE(ABS(B3:B7- $F$4)) * (5)^0.5</f>
+        <v>1.7888543819998323E-2</v>
+      </c>
+      <c r="G5" s="2" cm="1">
+        <f t="array" ref="G5">AVERAGE(ABS(C3:C7- $F$4)) * (5)^0.5</f>
+        <v>3.1304951684997057E-2</v>
+      </c>
+      <c r="H5" s="2" cm="1">
+        <f t="array" ref="H5">AVERAGE((B3:B7 - H$4)^2) ^ 0.5 * (5)^0.5</f>
+        <v>2.3452078799117149E-2</v>
+      </c>
+      <c r="I5" s="2" cm="1">
+        <f t="array" ref="I5">AVERAGE((C3:C7 - I$4)^2) ^ 0.5 * (5)^0.5</f>
+        <v>4.0373258476372707E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.01</v>
-      </c>
-      <c r="C6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7">
         <v>0.02</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="C6" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D6" s="2"/>
       <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
         <f>F5*(3.14 / 2)^0.5</f>
-        <v>0.15849290204927161</v>
-      </c>
-      <c r="G6" s="3">
+        <v>2.2414281161795044E-2</v>
+      </c>
+      <c r="G6" s="2">
         <f>G5*(3.14 / 2)^0.5</f>
-        <v>0.27736257858622526</v>
-      </c>
-      <c r="H6" s="3">
+        <v>3.9224992033141316E-2</v>
+      </c>
+      <c r="H6" s="2">
         <f>H5</f>
-        <v>0.16583123951776998</v>
-      </c>
-      <c r="I6" s="3">
+        <v>2.3452078799117149E-2</v>
+      </c>
+      <c r="I6" s="2">
         <f>I5</f>
-        <v>0.28548204847240399</v>
+        <v>4.0373258476372707E-2</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="C7" s="8">
-        <v>-0.01</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="C7" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8">
-        <v>0.02</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="C9" s="8">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="I9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="I9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.03</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" t="s">
         <v>1</v>
@@ -709,7 +732,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" t="s">
         <v>1</v>
@@ -718,227 +741,235 @@
         <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" s="8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.01</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2">
         <v>0.46678900000000001</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>0.53321099999999999</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="3">
         <f>SUM(F11:G11)</f>
         <v>1</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="3">
         <v>0.75226099999999996</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="3">
         <v>0.24773899999999999</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="3">
         <f>SUM(I11:J11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" s="8">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="C12" s="8">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2.75E-2</v>
+      </c>
+      <c r="C12" s="7">
         <v>0.03</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="5">
-        <f>$B11*F$11</f>
+      <c r="F12" s="3">
+        <f>$B9*F$11</f>
         <v>7.0018349999999997E-3</v>
       </c>
-      <c r="G12" s="5">
-        <f>$C11*G$11</f>
+      <c r="G12" s="3">
+        <f>$C9*G$11</f>
         <v>5.3321100000000001E-3</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="3">
         <f>SUM(F12:G12)</f>
         <v>1.2333944999999999E-2</v>
       </c>
-      <c r="I12" s="5">
-        <f>$B11*I$11</f>
+      <c r="I12" s="3">
+        <f>$B9*I$11</f>
         <v>1.1283914999999999E-2</v>
       </c>
-      <c r="J12" s="5">
-        <f>$C11*J$11</f>
+      <c r="J12" s="3">
+        <f>$C9*J$11</f>
         <v>2.4773899999999999E-3</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="3">
         <f>SUM(I12:J12)</f>
         <v>1.3761304999999998E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" s="8">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5">
-        <f t="shared" ref="F13:G16" si="0">$B12*F$11</f>
+        <v>10</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="3">
+        <f>$B10*F$11</f>
         <v>1.1669725000000001E-2</v>
       </c>
-      <c r="G13" s="5">
-        <f t="shared" ref="G13:G16" si="1">$C12*G$11</f>
+      <c r="G13" s="3">
+        <f>$C10*G$11</f>
         <v>1.599633E-2</v>
       </c>
-      <c r="H13" s="5">
-        <f t="shared" ref="H13:H16" si="2">SUM(F13:G13)</f>
+      <c r="H13" s="3">
+        <f t="shared" ref="H13:H16" si="0">SUM(F13:G13)</f>
         <v>2.7666055000000002E-2</v>
       </c>
-      <c r="I13" s="5">
-        <f t="shared" ref="I13:I16" si="3">$B12*I$11</f>
+      <c r="I13" s="3">
+        <f>$B10*I$11</f>
         <v>1.8806525000000001E-2</v>
       </c>
-      <c r="J13" s="5">
-        <f t="shared" ref="J13:J16" si="4">$C12*J$11</f>
+      <c r="J13" s="3">
+        <f>$C10*J$11</f>
         <v>7.4321699999999992E-3</v>
       </c>
-      <c r="K13" s="5">
-        <f t="shared" ref="K13:K16" si="5">SUM(I13:J13)</f>
+      <c r="K13" s="3">
+        <f t="shared" ref="K13:K16" si="1">SUM(I13:J13)</f>
         <v>2.6238694999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2.75E-2</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0.03</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5">
+      <c r="E14" s="6"/>
+      <c r="F14" s="3">
+        <f>$B11*F$11</f>
+        <v>8.1688075000000016E-3</v>
+      </c>
+      <c r="G14" s="3">
+        <f>$C11*G$11</f>
+        <v>-2.6660550000000001E-3</v>
+      </c>
+      <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>8.1688075000000016E-3</v>
-      </c>
-      <c r="G14" s="5">
+        <v>5.5027525000000011E-3</v>
+      </c>
+      <c r="I14" s="3">
+        <f>$B11*I$11</f>
+        <v>1.31645675E-2</v>
+      </c>
+      <c r="J14" s="3">
+        <f>$C11*J$11</f>
+        <v>-1.2386949999999999E-3</v>
+      </c>
+      <c r="K14" s="3">
         <f t="shared" si="1"/>
-        <v>-2.6660550000000001E-3</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="2"/>
-        <v>5.5027525000000011E-3</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="3"/>
-        <v>1.31645675E-2</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="4"/>
-        <v>-1.2386949999999999E-3</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="5"/>
         <v>1.19258725E-2</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" s="8">
-        <v>1.8749999999999999E-2</v>
-      </c>
-      <c r="C15" s="8">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5">
+      <c r="E15" s="6"/>
+      <c r="F15" s="3">
+        <f>$B12*F$11</f>
+        <v>1.2836697500000001E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <f>$C12*G$11</f>
+        <v>1.599633E-2</v>
+      </c>
+      <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>1.2836697500000001E-2</v>
-      </c>
-      <c r="G15" s="5">
+        <v>2.88330275E-2</v>
+      </c>
+      <c r="I15" s="3">
+        <f>$B12*I$11</f>
+        <v>2.0687177499999997E-2</v>
+      </c>
+      <c r="J15" s="3">
+        <f>$C12*J$11</f>
+        <v>7.4321699999999992E-3</v>
+      </c>
+      <c r="K15" s="3">
         <f t="shared" si="1"/>
-        <v>1.599633E-2</v>
-      </c>
-      <c r="H15" s="5">
-        <f t="shared" si="2"/>
-        <v>2.88330275E-2</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="3"/>
-        <v>2.0687177499999997E-2</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="4"/>
-        <v>7.4321699999999992E-3</v>
-      </c>
-      <c r="K15" s="5">
-        <f t="shared" si="5"/>
         <v>2.8119347499999996E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E16" s="4"/>
-      <c r="F16" s="5">
+      <c r="E16" s="6"/>
+      <c r="F16" s="3">
+        <f>$B13*F$11</f>
+        <v>7.4686240000000001E-3</v>
+      </c>
+      <c r="G16" s="3">
+        <f>$C13*G$11</f>
+        <v>2.3994494999999998E-2</v>
+      </c>
+      <c r="H16" s="3">
         <f t="shared" si="0"/>
-        <v>8.7522937499999991E-3</v>
-      </c>
-      <c r="G16" s="5">
+        <v>3.1463118999999998E-2</v>
+      </c>
+      <c r="I16" s="3">
+        <f>$B13*I$11</f>
+        <v>1.2036175999999999E-2</v>
+      </c>
+      <c r="J16" s="3">
+        <f>$C13*J$11</f>
+        <v>1.1148254999999999E-2</v>
+      </c>
+      <c r="K16" s="3">
         <f t="shared" si="1"/>
-        <v>2.3994494999999998E-2</v>
-      </c>
-      <c r="H16" s="5">
-        <f t="shared" si="2"/>
-        <v>3.2746788749999999E-2</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="3"/>
-        <v>1.4104893749999998E-2</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="4"/>
-        <v>1.1148254999999999E-2</v>
-      </c>
-      <c r="K16" s="5">
-        <f t="shared" si="5"/>
-        <v>2.5253148749999996E-2</v>
+        <v>2.3184430999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="6" cm="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="4" cm="1">
         <f t="array" ref="H17">PRODUCT(1 + H12:H16) * 100</f>
-        <v>111.14702062969199</v>
-      </c>
-      <c r="K17" s="6" cm="1">
+        <v>111.008868596939</v>
+      </c>
+      <c r="K17" s="4" cm="1">
         <f t="array" ref="K17">PRODUCT(1 + K12:K16) * 100</f>
-        <v>110.97047369324639</v>
+        <v>110.7465615902355</v>
+      </c>
+    </row>
+    <row r="18" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2">
+        <f>STDEV(H12:H16)* (5)^0.5</f>
+        <v>2.5748956525065814E-2</v>
+      </c>
+      <c r="K18" s="2">
+        <f>STDEV(K12:K16) * (5)^0.5</f>
+        <v>1.6470141202926218E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" cm="1">
+        <f t="array" ref="H19">AVERAGE(ABS(H12:H16-AVERAGE(H12:H16))) * (5)^0.5</f>
+        <v>2.1898137575741303E-2</v>
+      </c>
+      <c r="K19" s="2" cm="1">
+        <f t="array" ref="K19">AVERAGE(ABS(K12:K16-AVERAGE(K12:K16))) * (5)^0.5</f>
+        <v>1.395725269269142E-2</v>
       </c>
     </row>
   </sheetData>
